--- a/docs/CEP_Tenant_Onboarding_and_Sending_Setup.xlsx
+++ b/docs/CEP_Tenant_Onboarding_and_Sending_Setup.xlsx
@@ -584,7 +584,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>3. Outlook for Windows ignores media queries: a block set to Hide on Desktop still shows there.</t>
+          <t>3. Hide on Desktop is hidden everywhere by default and revealed on phones, so Outlook for Windows hides it; a phone app that ignores screen-size rules (Gmail with a non-Google account) hides it too.</t>
         </is>
       </c>
     </row>

--- a/docs/CEP_Tenant_Onboarding_and_Sending_Setup.xlsx
+++ b/docs/CEP_Tenant_Onboarding_and_Sending_Setup.xlsx
@@ -846,17 +846,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Back-office → Email server</t>
+          <t>Back-office → Mail server</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>An SMTP server the platform uses for its own notifications, shareable with workspaces as a campaign sender.</t>
+          <t>An SMTP server for the platform's own mail only: alerts, password links, and the fallback for a workspace that has not entered its own server yet.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Optional: a workspace can bring its own engine instead (sheet 3).</t>
+          <t>Never a workspace's sending engine: every workspace enters its own mail server or sending engine (sheet 3).</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Also usable as the platform's shared server (back-office).</t>
+          <t>Each workspace has its own; the platform's server is not offered.</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
